--- a/docs/Mapping_casi_uso/cittadinanza/Citt_999.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="101">
   <si>
     <t>Sezione</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Intestatario</t>
@@ -367,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -657,19 +663,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -680,16 +686,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>40</v>
@@ -703,16 +709,16 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -726,7 +732,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -735,7 +741,7 @@
         <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -749,16 +755,16 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -772,7 +778,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
@@ -781,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -795,7 +801,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
@@ -804,7 +810,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -818,7 +824,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
@@ -827,7 +833,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -841,16 +847,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -864,7 +870,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
@@ -873,7 +879,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -887,7 +893,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
@@ -896,7 +902,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -910,7 +916,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>59</v>
@@ -919,7 +925,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>60</v>
@@ -933,7 +939,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>61</v>
@@ -942,7 +948,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>62</v>
@@ -956,16 +962,16 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>64</v>
@@ -979,7 +985,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
@@ -988,7 +994,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>66</v>
@@ -1002,16 +1008,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>68</v>
@@ -1025,7 +1031,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>69</v>
@@ -1034,7 +1040,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>70</v>
@@ -1048,7 +1054,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
@@ -1057,7 +1063,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>72</v>
@@ -1071,7 +1077,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>73</v>
@@ -1080,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>74</v>
@@ -1094,7 +1100,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>75</v>
@@ -1103,7 +1109,7 @@
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>76</v>
@@ -1117,7 +1123,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>77</v>
@@ -1126,7 +1132,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>78</v>
@@ -1140,7 +1146,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>79</v>
@@ -1149,7 +1155,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>80</v>
@@ -1163,7 +1169,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>81</v>
@@ -1172,7 +1178,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>82</v>
@@ -1186,7 +1192,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>83</v>
@@ -1195,7 +1201,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>84</v>
@@ -1209,7 +1215,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>85</v>
@@ -1218,7 +1224,7 @@
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>86</v>
@@ -1232,7 +1238,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
@@ -1241,7 +1247,7 @@
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>88</v>
@@ -1255,7 +1261,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>89</v>
@@ -1264,7 +1270,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>90</v>
@@ -1278,16 +1284,16 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>92</v>
@@ -1301,7 +1307,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>93</v>
@@ -1310,7 +1316,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>94</v>
@@ -1324,16 +1330,16 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>96</v>
@@ -1347,16 +1353,16 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>98</v>
@@ -1365,6 +1371,29 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/cittadinanza/Citt_999.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="107">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -385,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -444,63 +450,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -509,90 +515,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -601,21 +607,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -624,12 +630,12 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -638,7 +644,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -647,21 +653,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -670,21 +676,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -693,44 +699,44 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -739,21 +745,21 @@
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -762,21 +768,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -785,12 +791,12 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
@@ -799,7 +805,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -808,21 +814,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -831,21 +837,21 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -854,12 +860,12 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
@@ -868,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -877,21 +883,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -900,21 +906,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -923,21 +929,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>60</v>
@@ -946,21 +952,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>62</v>
@@ -969,21 +975,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>64</v>
@@ -992,21 +998,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>66</v>
@@ -1015,21 +1021,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>68</v>
@@ -1038,12 +1044,12 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>69</v>
@@ -1052,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>70</v>
@@ -1061,21 +1067,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>72</v>
@@ -1084,21 +1090,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>74</v>
@@ -1107,21 +1113,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>76</v>
@@ -1130,21 +1136,21 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>78</v>
@@ -1153,21 +1159,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>80</v>
@@ -1176,21 +1182,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>82</v>
@@ -1199,21 +1205,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>84</v>
@@ -1222,21 +1228,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>86</v>
@@ -1245,21 +1251,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>88</v>
@@ -1268,21 +1274,21 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>90</v>
@@ -1291,21 +1297,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>92</v>
@@ -1314,21 +1320,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>94</v>
@@ -1337,21 +1343,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>96</v>
@@ -1360,12 +1366,12 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>97</v>
@@ -1374,7 +1380,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>98</v>
@@ -1383,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>100</v>
@@ -1406,21 +1412,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>102</v>
@@ -1429,12 +1435,12 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>103</v>
@@ -1443,7 +1449,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>104</v>
@@ -1452,7 +1458,30 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
